--- a/outputs/daily/hr_rankings_2026-09-03_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-03_full.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -31552,7 +31552,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -33496,7 +33496,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -35156,7 +35156,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -39868,7 +39868,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -41816,7 +41816,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -46570,7 +46570,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -46850,7 +46850,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -47130,7 +47130,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -51282,7 +51282,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
